--- a/ABC突破切線圖表_20260611/ABC突破切線精選_20260611.xlsx
+++ b/ABC突破切線圖表_20260611/ABC突破切線精選_20260611.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -557,30 +557,30 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>9914.TW</t>
+          <t>3576.TW</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>美利達</t>
+          <t>聯合再生</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>73.7</v>
+        <v>18.25</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>17.17</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>5.89%</t>
+          <t>6.26%</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>4777</v>
+        <v>57019</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
@@ -591,32 +591,66 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>6239.TW</t>
+          <t>5521.TW</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>工信</t>
         </is>
       </c>
       <c r="C3" s="9" t="n">
-        <v>333</v>
+        <v>11.25</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>326.25</v>
+        <v>10.37</v>
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="F3" s="11" t="n">
-        <v>17412</v>
+        <v>10131</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2243.TW</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>宏旭-KY</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>5.12%</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2117</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>點我查看</t>
         </is>
@@ -626,6 +660,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
